--- a/工作目录/01_预处理/output_30s_step5s/alignment_summary.xlsx
+++ b/工作目录/01_预处理/output_30s_step5s/alignment_summary.xlsx
@@ -1950,7 +1950,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>hr_first</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>367</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -7331,23 +7331,23 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>hr_first</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46128.76806712963</v>
+        <v>46128.76739719907</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>46128.76835042317</v>
+        <v>46128.78891222728</v>
       </c>
       <c r="J29" t="n">
-        <v>24.4765625</v>
+        <v>1858.8984375</v>
       </c>
       <c r="K29" t="n">
         <v>256</v>
       </c>
       <c r="L29" t="n">
-        <v>6266</v>
+        <v>475878</v>
       </c>
       <c r="M29" s="1" t="n">
         <v>46128.76806712963</v>
@@ -7359,13 +7359,13 @@
         <v>373</v>
       </c>
       <c r="P29" t="n">
-        <v>6</v>
+        <v>361</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>57.882</v>
       </c>
       <c r="R29" t="n">
-        <v>1833.523437</v>
+        <v>56.983562</v>
       </c>
       <c r="S29" t="n">
         <v>1875.576</v>
@@ -7376,11 +7376,11 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>367</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>check_large_duration_gap</t>
+          <t>good_eye_anchor</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
